--- a/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,48</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>31,63</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,06</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>14,1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,82</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>22,25</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,39; 12,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,63; 17,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,77; 40,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,72; 10,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,66; 16,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,54; 22,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,23; 10,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,75; 15,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,84; 28,4</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>180,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,56%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,35; 79,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,79; 119,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>110,65; 272,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,82; 20,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,47; 32,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,95; 44,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,21; 30,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,48; 47,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,08; 85,1</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,14</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>25,23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,23</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>19,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,23; 13,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,75; 22,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,35; 32,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,9; 5,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,23; 6,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,45; 11,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,82; 9,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,65; 15,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,31; 24,26</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,91; 33,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,84; 57,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,93; 82,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,14; 6,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,38; 7,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,94; 13,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,86; 15,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,63; 24,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,44; 40,18</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>16,1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>25,93</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>35,99</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,32</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>19,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,0; 21,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,26; 31,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,11; 41,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,57; 3,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,28; 5,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,91; 6,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,35; 11,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,02; 16,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,2; 23,0</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,6; 55,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,47; 82,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,07; 108,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,66; 4,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,3; 5,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,0; 7,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,18; 17,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,2; 25,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,86; 34,78</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>15,54</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>26,29</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>19,64</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,84</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,79; 21,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,47; 32,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,49; 41,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,7; 2,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,56; 3,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,1; 5,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,1; 11,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,87; 18,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,15; 23,49</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,93%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,07; 73,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,46; 112,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-33,38; 131,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,87; 2,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,65; 3,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,17; 6,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,69; 19,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,15; 29,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-24,37; 37,42</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>25,72</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>43,48</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-4,55</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,99</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>22,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,16; 19,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,87; 31,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,51; 49,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,12; -0,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,15; 3,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,06; 4,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,15; 8,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,0; 17,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,11; 26,06</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>101,39%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>171,38%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,81%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,56; 89,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,28; 145,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>126,25; 226,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,47; -0,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,23; 4,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,09; 5,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,8; 14,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,65; 29,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,47; 45,4</t>
         </is>
       </c>
     </row>
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-3,61</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,86</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>23,07</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,16</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,1; 3,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,11; 13,66</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,25; 29,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,73; 2,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,67; 7,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,31; 12,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,73; 2,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,02; 8,99</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,17; 26,95</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-9,08%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,41%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-27,43; 10,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,78; 37,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,32; 82,77</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,36; 3,06</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,73; 8,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,57; 13,95</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,32; 3,71</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,47; 14,07</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,34; 42,69</t>
         </is>
       </c>
     </row>
@@ -1920,47 +1920,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-4,88</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>13,74</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-11,28</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,86</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-8,95</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,87</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,27; 3,15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,43; 10,91</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,5; 22,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,6; -3,73</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,62; 4,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,49; 10,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,95; -2,7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,08; 4,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,81; 13,34</t>
         </is>
       </c>
     </row>
@@ -2026,47 +2026,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-13,77%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-16,09%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,08%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-15,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-1,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-36,54; 9,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,95; 36,37</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,5; 77,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-25,22; -5,46</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,23; 7,12</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,99; 16,66</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-24,83; -4,74</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,59; 8,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,77; 25,42</t>
         </is>
       </c>
     </row>
@@ -2136,47 +2136,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,92</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>27,11</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>11,13</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,99; 11,99</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,18; 21,09</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,96; 32,59</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,25; 1,38</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,64; 5,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,81; 9,37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,73; 6,16</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,59; 12,75</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,8; 20,9</t>
         </is>
       </c>
     </row>
@@ -2242,47 +2242,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,64%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,42; 36,42</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,58; 64,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,95; 97,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,65; 1,67</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,93; 6,15</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,81; 11,19</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,55; 10,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,77; 21,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,69; 35,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,63</t>
+          <t>31,39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>14,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22,25</t>
+          <t>22,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,17</t>
+          <t>1,38; 12,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 17,36</t>
+          <t>5,62; 17,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,77; 40,67</t>
+          <t>22,09; 39,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 10,54</t>
+          <t>-2,02; 11,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 16,44</t>
+          <t>3,57; 16,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 22,77</t>
+          <t>6,28; 22,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,08</t>
+          <t>0,4; 9,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 15,26</t>
+          <t>5,91; 15,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 28,4</t>
+          <t>16,7; 29,2</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180,89%</t>
+          <t>179,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 79,88</t>
+          <t>6,25; 82,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,79; 119,35</t>
+          <t>27,6; 117,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110,65; 272,73</t>
+          <t>111,97; 266,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 20,78</t>
+          <t>-3,5; 21,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 32,17</t>
+          <t>6,37; 32,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 44,78</t>
+          <t>11,45; 45,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 30,62</t>
+          <t>0,98; 30,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 47,56</t>
+          <t>15,58; 47,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,08; 85,1</t>
+          <t>45,99; 86,66</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,23</t>
+          <t>23,41</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,46</t>
+          <t>6,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>17,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,2</t>
+          <t>2,95; 12,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,75; 22,56</t>
+          <t>11,72; 22,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 32,53</t>
+          <t>16,64; 30,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 5,62</t>
+          <t>-1,67; 5,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 6,07</t>
+          <t>-1,47; 6,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 11,52</t>
+          <t>2,18; 10,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,55</t>
+          <t>1,95; 9,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,07</t>
+          <t>7,59; 14,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,31; 24,26</t>
+          <t>12,39; 20,7</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 33,22</t>
+          <t>6,63; 32,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,84; 57,72</t>
+          <t>26,05; 56,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,93; 82,59</t>
+          <t>37,39; 77,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 6,74</t>
+          <t>-1,89; 7,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 7,36</t>
+          <t>-1,65; 7,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 13,75</t>
+          <t>2,55; 12,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 15,82</t>
+          <t>3,04; 14,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,63; 24,64</t>
+          <t>11,74; 24,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,44; 40,18</t>
+          <t>19,62; 34,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35,99</t>
+          <t>34,34</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,57</t>
+          <t>18,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,0; 21,36</t>
+          <t>10,65; 21,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,26; 31,1</t>
+          <t>20,89; 31,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,11; 41,2</t>
+          <t>28,41; 39,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,93</t>
+          <t>-1,54; 4,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,43</t>
+          <t>0,6; 5,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,6</t>
+          <t>1,85; 6,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,53</t>
+          <t>4,39; 11,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,02; 16,99</t>
+          <t>9,55; 16,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,2; 23,0</t>
+          <t>15,03; 21,47</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,6; 55,87</t>
+          <t>24,22; 57,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,47; 82,72</t>
+          <t>47,08; 84,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67,07; 108,77</t>
+          <t>64,69; 105,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,31</t>
+          <t>-1,64; 4,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,92</t>
+          <t>0,64; 6,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,22</t>
+          <t>1,96; 6,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,18; 17,43</t>
+          <t>6,32; 17,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 25,63</t>
+          <t>13,78; 25,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,86; 34,78</t>
+          <t>21,41; 32,75</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19,64</t>
+          <t>39,19</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,18</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,07</t>
+          <t>21,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,79; 21,61</t>
+          <t>8,98; 21,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,47; 32,57</t>
+          <t>20,37; 31,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 41,76</t>
+          <t>33,57; 45,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,5</t>
+          <t>-3,98; 2,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,67</t>
+          <t>-1,45; 3,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,78</t>
+          <t>0,88; 5,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 11,83</t>
+          <t>3,54; 11,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 18,02</t>
+          <t>10,33; 18,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 23,49</t>
+          <t>17,9; 25,0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>118,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,07; 73,97</t>
+          <t>24,29; 73,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56,46; 112,51</t>
+          <t>55,86; 108,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 131,35</t>
+          <t>89,77; 152,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,7</t>
+          <t>-4,16; 2,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,99</t>
+          <t>-1,52; 4,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,32</t>
+          <t>0,92; 5,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 19,38</t>
+          <t>5,34; 19,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,15; 29,62</t>
+          <t>15,73; 29,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 37,42</t>
+          <t>26,81; 40,59</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43,48</t>
+          <t>43,32</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22,06</t>
+          <t>22,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,16; 19,57</t>
+          <t>6,32; 18,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,87; 31,75</t>
+          <t>19,29; 32,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37,51; 49,48</t>
+          <t>37,32; 48,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,12; -0,73</t>
+          <t>-8,0; -0,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,95</t>
+          <t>-2,28; 3,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,9</t>
+          <t>0,16; 5,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 8,63</t>
+          <t>-0,23; 8,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,0; 17,24</t>
+          <t>8,43; 17,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,11; 26,06</t>
+          <t>18,36; 26,69</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171,38%</t>
+          <t>170,76%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21,56; 89,08</t>
+          <t>22,87; 87,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>66,28; 145,07</t>
+          <t>66,55; 143,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126,25; 226,74</t>
+          <t>125,89; 224,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -0,77</t>
+          <t>-8,45; -0,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,27</t>
+          <t>-2,37; 3,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,34</t>
+          <t>0,18; 5,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 14,74</t>
+          <t>-0,26; 15,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12,65; 29,74</t>
+          <t>13,43; 30,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,47; 45,4</t>
+          <t>28,74; 46,71</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23,07</t>
+          <t>22,82</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17,16</t>
+          <t>12,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 3,94</t>
+          <t>-10,93; 4,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 13,66</t>
+          <t>-1,29; 14,87</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16,25; 29,46</t>
+          <t>15,35; 30,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 2,68</t>
+          <t>-7,06; 2,71</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 7,65</t>
+          <t>-0,57; 7,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,31; 12,07</t>
+          <t>1,29; 8,32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 2,36</t>
+          <t>-8,49; 2,33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,99</t>
+          <t>-1,05; 9,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,17; 26,95</t>
+          <t>8,47; 16,95</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 10,78</t>
+          <t>-25,49; 12,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 37,86</t>
+          <t>-3,03; 42,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35,32; 82,77</t>
+          <t>34,2; 88,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 3,06</t>
+          <t>-7,72; 3,03</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 8,75</t>
+          <t>-0,62; 8,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,57; 13,95</t>
+          <t>1,41; 9,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 3,71</t>
+          <t>-12,19; 3,57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 14,07</t>
+          <t>-1,5; 14,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16,34; 42,69</t>
+          <t>12,08; 26,82</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,68</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>7,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 3,15</t>
+          <t>-13,73; 4,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 10,91</t>
+          <t>-5,55; 11,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,5; 22,12</t>
+          <t>5,49; 21,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-18,6; -3,73</t>
+          <t>-18,78; -3,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 4,59</t>
+          <t>-10,67; 4,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,96</t>
+          <t>-1,56; 10,38</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-14,95; -2,7</t>
+          <t>-15,98; -2,7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 4,58</t>
+          <t>-7,11; 4,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,81; 13,34</t>
+          <t>2,66; 12,58</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 9,98</t>
+          <t>-34,0; 14,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 36,37</t>
+          <t>-13,73; 35,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,5; 77,42</t>
+          <t>13,51; 71,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,22; -5,46</t>
+          <t>-25,25; -5,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 7,12</t>
+          <t>-14,54; 6,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 16,66</t>
+          <t>-2,09; 15,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -4,74</t>
+          <t>-26,05; -5,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 8,59</t>
+          <t>-11,75; 9,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4,77; 25,42</t>
+          <t>4,33; 23,65</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27,11</t>
+          <t>31,28</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,48</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>17,45</t>
+          <t>18,9</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,99</t>
+          <t>6,86; 11,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>16,18; 21,09</t>
+          <t>16,48; 21,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11,96; 32,59</t>
+          <t>28,77; 33,56</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,38</t>
+          <t>-2,22; 1,43</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,1</t>
+          <t>1,57; 4,96</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,37</t>
+          <t>4,99; 8,16</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,16</t>
+          <t>2,91; 6,23</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>9,59; 12,75</t>
+          <t>9,43; 12,76</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>8,8; 20,9</t>
+          <t>17,31; 20,54</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>19,42; 36,42</t>
+          <t>19,42; 35,92</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>45,58; 64,3</t>
+          <t>46,31; 64,22</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>35,95; 97,21</t>
+          <t>80,67; 101,88</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,67</t>
+          <t>-2,63; 1,71</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,15</t>
+          <t>1,85; 5,96</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,19</t>
+          <t>5,86; 9,83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,5</t>
+          <t>4,79; 10,62</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15,77; 21,72</t>
+          <t>15,58; 21,74</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>14,69; 35,4</t>
+          <t>28,61; 35,25</t>
         </is>
       </c>
     </row>
